--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4150,7 +4150,7 @@
         <v>103769665</v>
       </c>
       <c r="B33" t="n">
-        <v>89235</v>
+        <v>89237</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4150,7 +4150,7 @@
         <v>103769665</v>
       </c>
       <c r="B33" t="n">
-        <v>89237</v>
+        <v>89239</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 6264-2024 artfynd.xlsx
+++ b/artfynd/A 6264-2024 artfynd.xlsx
@@ -4150,7 +4150,7 @@
         <v>103769665</v>
       </c>
       <c r="B33" t="n">
-        <v>89239</v>
+        <v>89241</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
